--- a/artfynd/A 40107-2023 artfynd.xlsx
+++ b/artfynd/A 40107-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40107-2023 artfynd.xlsx
+++ b/artfynd/A 40107-2023 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80499463</v>
+        <v>80499445</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533242.8890863246</v>
+        <v>533243</v>
       </c>
       <c r="R2" t="n">
-        <v>7061793.051367498</v>
+        <v>7061793</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +746,9 @@
           <t>2019-06-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +779,7 @@
         <v>80499403</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533392.9867530019</v>
+        <v>533393</v>
       </c>
       <c r="R3" t="n">
-        <v>7061719.184528683</v>
+        <v>7061719</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +847,9 @@
           <t>2019-06-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-06-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,42 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80499445</v>
+        <v>80499463</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533242.8890863246</v>
+        <v>533243</v>
       </c>
       <c r="R4" t="n">
-        <v>7061793.051367498</v>
+        <v>7061793</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +949,9 @@
           <t>2019-06-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 40107-2023 artfynd.xlsx
+++ b/artfynd/A 40107-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80499445</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80499403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80499463</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>